--- a/data/nzd0192/nzd0192.xlsx
+++ b/data/nzd0192/nzd0192.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M720"/>
+  <dimension ref="A1:M726"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32846,6 +32846,276 @@
         <v>353.26</v>
       </c>
       <c r="M720" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-27 21:59:12+00:00</t>
+        </is>
+      </c>
+      <c r="B721" t="n">
+        <v>334.71</v>
+      </c>
+      <c r="C721" t="n">
+        <v>335.79</v>
+      </c>
+      <c r="D721" t="n">
+        <v>337.82</v>
+      </c>
+      <c r="E721" t="n">
+        <v>340.14</v>
+      </c>
+      <c r="F721" t="n">
+        <v>344.43</v>
+      </c>
+      <c r="G721" t="n">
+        <v>355.38</v>
+      </c>
+      <c r="H721" t="n">
+        <v>369.1</v>
+      </c>
+      <c r="I721" t="n">
+        <v>363.44</v>
+      </c>
+      <c r="J721" t="n">
+        <v>359.39</v>
+      </c>
+      <c r="K721" t="n">
+        <v>353.58</v>
+      </c>
+      <c r="L721" t="n">
+        <v>352.96</v>
+      </c>
+      <c r="M721" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B722" t="n">
+        <v>333.12</v>
+      </c>
+      <c r="C722" t="n">
+        <v>335.7</v>
+      </c>
+      <c r="D722" t="n">
+        <v>338.48</v>
+      </c>
+      <c r="E722" t="n">
+        <v>340.03</v>
+      </c>
+      <c r="F722" t="n">
+        <v>345.11</v>
+      </c>
+      <c r="G722" t="n">
+        <v>356.06</v>
+      </c>
+      <c r="H722" t="n">
+        <v>370.01</v>
+      </c>
+      <c r="I722" t="n">
+        <v>363.53</v>
+      </c>
+      <c r="J722" t="n">
+        <v>358.61</v>
+      </c>
+      <c r="K722" t="n">
+        <v>352.99</v>
+      </c>
+      <c r="L722" t="n">
+        <v>352.74</v>
+      </c>
+      <c r="M722" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B723" t="n">
+        <v>332.34</v>
+      </c>
+      <c r="C723" t="n">
+        <v>335.15</v>
+      </c>
+      <c r="D723" t="n">
+        <v>339.25</v>
+      </c>
+      <c r="E723" t="n">
+        <v>339.52</v>
+      </c>
+      <c r="F723" t="n">
+        <v>344.35</v>
+      </c>
+      <c r="G723" t="n">
+        <v>355.32</v>
+      </c>
+      <c r="H723" t="n">
+        <v>368.83</v>
+      </c>
+      <c r="I723" t="n">
+        <v>363.47</v>
+      </c>
+      <c r="J723" t="n">
+        <v>357.04</v>
+      </c>
+      <c r="K723" t="n">
+        <v>350.98</v>
+      </c>
+      <c r="L723" t="n">
+        <v>352.02</v>
+      </c>
+      <c r="M723" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:59:16+00:00</t>
+        </is>
+      </c>
+      <c r="B724" t="n">
+        <v>332.34</v>
+      </c>
+      <c r="C724" t="n">
+        <v>335.15</v>
+      </c>
+      <c r="D724" t="n">
+        <v>339.25</v>
+      </c>
+      <c r="E724" t="n">
+        <v>339.41</v>
+      </c>
+      <c r="F724" t="n">
+        <v>344.35</v>
+      </c>
+      <c r="G724" t="n">
+        <v>355.32</v>
+      </c>
+      <c r="H724" t="n">
+        <v>368.83</v>
+      </c>
+      <c r="I724" t="n">
+        <v>363.47</v>
+      </c>
+      <c r="J724" t="n">
+        <v>357.04</v>
+      </c>
+      <c r="K724" t="n">
+        <v>350.98</v>
+      </c>
+      <c r="L724" t="n">
+        <v>351.52</v>
+      </c>
+      <c r="M724" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B725" t="n">
+        <v>331.76</v>
+      </c>
+      <c r="C725" t="n">
+        <v>335.36</v>
+      </c>
+      <c r="D725" t="n">
+        <v>339.47</v>
+      </c>
+      <c r="E725" t="n">
+        <v>339.76</v>
+      </c>
+      <c r="F725" t="n">
+        <v>344.35</v>
+      </c>
+      <c r="G725" t="n">
+        <v>355.53</v>
+      </c>
+      <c r="H725" t="n">
+        <v>369.33</v>
+      </c>
+      <c r="I725" t="n">
+        <v>363.84</v>
+      </c>
+      <c r="J725" t="n">
+        <v>357.09</v>
+      </c>
+      <c r="K725" t="n">
+        <v>350.95</v>
+      </c>
+      <c r="L725" t="n">
+        <v>351.46</v>
+      </c>
+      <c r="M725" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B726" t="n">
+        <v>331.98</v>
+      </c>
+      <c r="C726" t="n">
+        <v>335.54</v>
+      </c>
+      <c r="D726" t="n">
+        <v>340.08</v>
+      </c>
+      <c r="E726" t="n">
+        <v>339.93</v>
+      </c>
+      <c r="F726" t="n">
+        <v>345.07</v>
+      </c>
+      <c r="G726" t="n">
+        <v>355.99</v>
+      </c>
+      <c r="H726" t="n">
+        <v>369.78</v>
+      </c>
+      <c r="I726" t="n">
+        <v>364.17</v>
+      </c>
+      <c r="J726" t="n">
+        <v>357.26</v>
+      </c>
+      <c r="K726" t="n">
+        <v>350.76</v>
+      </c>
+      <c r="L726" t="n">
+        <v>351.23</v>
+      </c>
+      <c r="M726" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -32862,7 +33132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B730"/>
+  <dimension ref="A1:B736"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40165,6 +40435,66 @@
       </c>
       <c r="B730" t="n">
         <v>-0.66</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-06-27 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B731" t="n">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B732" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B733" t="n">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-07-13 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B734" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B735" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>-0.32</v>
       </c>
     </row>
   </sheetData>
@@ -40333,28 +40663,28 @@
         <v>0.1845</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1502426781482964</v>
+        <v>0.1340696224364724</v>
       </c>
       <c r="J2" t="n">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="K2" t="n">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04773545837564652</v>
+        <v>0.03788818573193453</v>
       </c>
       <c r="M2" t="n">
-        <v>4.024608138014805</v>
+        <v>4.069794828445947</v>
       </c>
       <c r="N2" t="n">
-        <v>25.42504507273517</v>
+        <v>26.03026168808413</v>
       </c>
       <c r="O2" t="n">
-        <v>5.042325363632851</v>
+        <v>5.101986053301609</v>
       </c>
       <c r="P2" t="n">
-        <v>338.6648203678432</v>
+        <v>338.8383837203601</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -40411,28 +40741,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3076079028815945</v>
+        <v>0.2952331664134811</v>
       </c>
       <c r="J3" t="n">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="K3" t="n">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1081930357982409</v>
+        <v>0.1012021608203967</v>
       </c>
       <c r="M3" t="n">
-        <v>5.517281019454903</v>
+        <v>5.530625154367039</v>
       </c>
       <c r="N3" t="n">
-        <v>44.03774910219619</v>
+        <v>44.1467306317996</v>
       </c>
       <c r="O3" t="n">
-        <v>6.636094416311162</v>
+        <v>6.644300612690518</v>
       </c>
       <c r="P3" t="n">
-        <v>334.8099087217884</v>
+        <v>334.9426985047372</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -40489,28 +40819,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2087636366742749</v>
+        <v>0.1983009555054676</v>
       </c>
       <c r="J4" t="n">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="K4" t="n">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0713989499463239</v>
+        <v>0.06533460147024617</v>
       </c>
       <c r="M4" t="n">
-        <v>4.688875812236376</v>
+        <v>4.697735879873755</v>
       </c>
       <c r="N4" t="n">
-        <v>32.00410123256284</v>
+        <v>32.08178738346872</v>
       </c>
       <c r="O4" t="n">
-        <v>5.657216739047819</v>
+        <v>5.66407868796583</v>
       </c>
       <c r="P4" t="n">
-        <v>339.9040111787214</v>
+        <v>340.0162666996423</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -40567,28 +40897,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2643990716753497</v>
+        <v>0.2502180258703745</v>
       </c>
       <c r="J5" t="n">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="K5" t="n">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1045261843717604</v>
+        <v>0.09464120888343819</v>
       </c>
       <c r="M5" t="n">
-        <v>4.631479357011838</v>
+        <v>4.6632197071715</v>
       </c>
       <c r="N5" t="n">
-        <v>33.81475369636112</v>
+        <v>34.15652295494479</v>
       </c>
       <c r="O5" t="n">
-        <v>5.815045459526616</v>
+        <v>5.844358215830442</v>
       </c>
       <c r="P5" t="n">
-        <v>341.4438249149053</v>
+        <v>341.5959969639289</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -40645,28 +40975,28 @@
         <v>0.1235</v>
       </c>
       <c r="I6" t="n">
-        <v>0.249140173137282</v>
+        <v>0.2366104558396246</v>
       </c>
       <c r="J6" t="n">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="K6" t="n">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08642798487341652</v>
+        <v>0.07899922659604164</v>
       </c>
       <c r="M6" t="n">
-        <v>5.126309357885348</v>
+        <v>5.150186872528297</v>
       </c>
       <c r="N6" t="n">
-        <v>36.86970440617738</v>
+        <v>37.04662792303812</v>
       </c>
       <c r="O6" t="n">
-        <v>6.07204285279488</v>
+        <v>6.086594115187747</v>
       </c>
       <c r="P6" t="n">
-        <v>345.6098599780461</v>
+        <v>345.744760362865</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -40723,28 +41053,28 @@
         <v>0.1494</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1488040439443479</v>
+        <v>0.142948015774917</v>
       </c>
       <c r="J7" t="n">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="K7" t="n">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04946886792078509</v>
+        <v>0.0464353117568852</v>
       </c>
       <c r="M7" t="n">
-        <v>4.081709764918013</v>
+        <v>4.077067647506698</v>
       </c>
       <c r="N7" t="n">
-        <v>24.02273353075986</v>
+        <v>23.93062718421499</v>
       </c>
       <c r="O7" t="n">
-        <v>4.901299167645234</v>
+        <v>4.891894028309995</v>
       </c>
       <c r="P7" t="n">
-        <v>355.2098211624607</v>
+        <v>355.2726577416815</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -40801,28 +41131,28 @@
         <v>0.1153</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1632091947090029</v>
+        <v>0.166323371156888</v>
       </c>
       <c r="J8" t="n">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="K8" t="n">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04238578865606479</v>
+        <v>0.04468214380259805</v>
       </c>
       <c r="M8" t="n">
-        <v>4.569168617132386</v>
+        <v>4.543073881430561</v>
       </c>
       <c r="N8" t="n">
-        <v>33.97959048005498</v>
+        <v>33.73001039378573</v>
       </c>
       <c r="O8" t="n">
-        <v>5.829201530231647</v>
+        <v>5.807754333112389</v>
       </c>
       <c r="P8" t="n">
-        <v>362.9829766307603</v>
+        <v>362.949558351671</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -40879,28 +41209,28 @@
         <v>0.1881</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1108095813895328</v>
+        <v>0.1117847431162202</v>
       </c>
       <c r="J9" t="n">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="K9" t="n">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02941293815543977</v>
+        <v>0.03044841172181445</v>
       </c>
       <c r="M9" t="n">
-        <v>3.822020534569166</v>
+        <v>3.795068079558706</v>
       </c>
       <c r="N9" t="n">
-        <v>22.8775387074784</v>
+        <v>22.69171751666217</v>
       </c>
       <c r="O9" t="n">
-        <v>4.783047010795357</v>
+        <v>4.763582424673911</v>
       </c>
       <c r="P9" t="n">
-        <v>360.0584466522079</v>
+        <v>360.0479780500244</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -40957,28 +41287,28 @@
         <v>0.1177</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1240976849326437</v>
+        <v>0.1250929255582642</v>
       </c>
       <c r="J10" t="n">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="K10" t="n">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0237115012142699</v>
+        <v>0.02451114873273874</v>
       </c>
       <c r="M10" t="n">
-        <v>4.999722198225136</v>
+        <v>4.964242903380073</v>
       </c>
       <c r="N10" t="n">
-        <v>35.80181665780927</v>
+        <v>35.51568272659839</v>
       </c>
       <c r="O10" t="n">
-        <v>5.983461929168537</v>
+        <v>5.959503563770928</v>
       </c>
       <c r="P10" t="n">
-        <v>353.7697955117839</v>
+        <v>353.7591314829103</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -41035,28 +41365,28 @@
         <v>0.1328</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2077878869661772</v>
+        <v>0.2130984822442443</v>
       </c>
       <c r="J11" t="n">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="K11" t="n">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="L11" t="n">
-        <v>0.06123824881397888</v>
+        <v>0.0651522755785684</v>
       </c>
       <c r="M11" t="n">
-        <v>4.965919743762958</v>
+        <v>4.949867444954106</v>
       </c>
       <c r="N11" t="n">
-        <v>37.37073668987897</v>
+        <v>37.15934267057152</v>
       </c>
       <c r="O11" t="n">
-        <v>6.113160940943643</v>
+        <v>6.095846345715377</v>
       </c>
       <c r="P11" t="n">
-        <v>342.8103675696757</v>
+        <v>342.753402682652</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -41113,28 +41443,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2241580873982636</v>
+        <v>0.2314250655702023</v>
       </c>
       <c r="J12" t="n">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="K12" t="n">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="L12" t="n">
-        <v>0.08430532696056725</v>
+        <v>0.0904152351458658</v>
       </c>
       <c r="M12" t="n">
-        <v>4.438656884122985</v>
+        <v>4.429776675418267</v>
       </c>
       <c r="N12" t="n">
-        <v>30.81506426928226</v>
+        <v>30.72687374075466</v>
       </c>
       <c r="O12" t="n">
-        <v>5.551131800748588</v>
+        <v>5.543182636424192</v>
       </c>
       <c r="P12" t="n">
-        <v>341.4383963637854</v>
+        <v>341.3604307434683</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -41172,7 +41502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M720"/>
+  <dimension ref="A1:M726"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89411,6 +89741,408 @@
         </is>
       </c>
     </row>
+    <row r="721">
+      <c r="A721" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-27 21:59:12+00:00</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>-37.14539013024549,175.8793448098992</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>-37.14610037577671,175.87945765206007</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>-37.14680948772743,175.87958109035714</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>-37.14751598710921,175.87970754158744</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>-37.148220862247385,175.87983274529242</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>-37.14892604264366,175.88000828981998</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>-37.1496251310076,175.880213363645</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>-37.15032595167917,175.8803258958686</t>
+        </is>
+      </c>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>-37.151021458972444,175.8805396392312</t>
+        </is>
+      </c>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>-37.15172097098438,175.88075436366674</t>
+        </is>
+      </c>
+      <c r="L721" t="inlineStr">
+        <is>
+          <t>-37.15239108856456,175.88107694602877</t>
+        </is>
+      </c>
+      <c r="M721" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>-37.14539201622553,175.87932707600692</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>-37.146100482531324,175.87945664824568</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>-37.146808704852326,175.87958845172946</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>-37.14751610480138,175.87970631266415</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>-37.148220297917895,175.8798403639697</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>-37.14892556240333,175.8800159175583</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>-37.14962391462007,175.88022348958552</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>-37.15032573895795,175.8803268730685</t>
+        </is>
+      </c>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>-37.151023678634346,175.88053131207903</t>
+        </is>
+      </c>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>-37.151722857221195,175.8807481570889</t>
+        </is>
+      </c>
+      <c r="L722" t="inlineStr">
+        <is>
+          <t>-37.15239184862783,175.88107465985203</t>
+        </is>
+      </c>
+      <c r="M722" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>-37.14539294142233,175.87931837636128</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>-37.14610113492046,175.87945051382445</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>-37.14680779149747,175.87959703999692</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>-37.147516650464915,175.879700614929</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>-37.148220928639056,175.87983184897743</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>-37.148926085017784,175.88000761678427</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>-37.14962549191364,175.88021035924498</t>
+        </is>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>-37.15032588077211,175.88032622160188</t>
+        </is>
+      </c>
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>-37.151028146413644,175.8805145510147</t>
+        </is>
+      </c>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>-37.15172928321207,175.88072701264332</t>
+        </is>
+      </c>
+      <c r="L723" t="inlineStr">
+        <is>
+          <t>-37.152394336107335,175.88106717781872</t>
+        </is>
+      </c>
+      <c r="M723" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:59:16+00:00</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>-37.14539294142233,175.87931837636128</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>-37.14610113492046,175.87945051382445</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>-37.14680779149747,175.87959703999692</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>-37.147516768157004,175.87969938600568</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>-37.148220928639056,175.87983184897743</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>-37.148926085017784,175.88000761678427</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>-37.14962549191364,175.88021035924498</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>-37.15032588077211,175.88032622160188</t>
+        </is>
+      </c>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>-37.151028146413644,175.8805145510147</t>
+        </is>
+      </c>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>-37.15172928321207,175.88072701264332</t>
+        </is>
+      </c>
+      <c r="L724" t="inlineStr">
+        <is>
+          <t>-37.15239606352338,175.88106198196195</t>
+        </is>
+      </c>
+      <c r="M724" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>-37.14539362938878,175.87931190739383</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>-37.14610088582645,175.879452856058</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>-37.14680753053883,175.8795994937876</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>-37.14751639368211,175.87970329621615</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>-37.148220928639056,175.87983184897743</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>-37.14892593670833,175.88000997240934</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>-37.14962482356907,175.88021592294868</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>-37.150325006251464,175.8803302389793</t>
+        </is>
+      </c>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>-37.15102800412772,175.8805150848066</t>
+        </is>
+      </c>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>-37.15172937912234,175.88072669705454</t>
+        </is>
+      </c>
+      <c r="L725" t="inlineStr">
+        <is>
+          <t>-37.152396270813306,175.8810613584591</t>
+        </is>
+      </c>
+      <c r="M725" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>-37.14539336843603,175.8793143611401</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>-37.14610067231728,175.87945486368682</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>-37.14680680697142,175.87960629747977</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>-37.147516211794255,175.87970519546118</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>-37.14822033111376,175.87983991581223</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>-37.148925611839864,175.88001513234997</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>-37.14962422205876,175.88022093028192</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>-37.15032422627348,175.88033382204554</t>
+        </is>
+      </c>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>-37.15102752035554,175.88051689969902</t>
+        </is>
+      </c>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>-37.15172998655413,175.88072469832565</t>
+        </is>
+      </c>
+      <c r="L726" t="inlineStr">
+        <is>
+          <t>-37.152397065424594,175.8810589683649</t>
+        </is>
+      </c>
+      <c r="M726" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
